--- a/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="381">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -297,27 +297,9 @@
     <t>AUTOMATION</t>
   </si>
   <si>
-    <t>AUTO_OUTLE7B01</t>
-  </si>
-  <si>
-    <t>2025-10-23</t>
-  </si>
-  <si>
     <t>03004121400</t>
   </si>
   <si>
-    <t>AUTO_OUTLD43F4</t>
-  </si>
-  <si>
-    <t>03005594000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB8546</t>
-  </si>
-  <si>
-    <t>03006513700</t>
-  </si>
-  <si>
     <t>N02N02N02N02N02N02</t>
   </si>
   <si>
@@ -396,283 +378,790 @@
     <t>12323</t>
   </si>
   <si>
-    <t>AUTO_OUTL13CC5</t>
-  </si>
-  <si>
-    <t>03963427100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL69154</t>
-  </si>
-  <si>
-    <t>03967327100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4B2C3</t>
-  </si>
-  <si>
-    <t>03970126100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEF63F</t>
-  </si>
-  <si>
-    <t>03956560000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL9CE30</t>
-  </si>
-  <si>
-    <t>03960596200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL23D0A</t>
-  </si>
-  <si>
-    <t>03963382400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6345B</t>
-  </si>
-  <si>
-    <t>03156445000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6B743</t>
-  </si>
-  <si>
-    <t>03159977300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL70B03</t>
-  </si>
-  <si>
-    <t>03162907600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL30C0A</t>
-  </si>
-  <si>
-    <t>03857510200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6C1F3</t>
-  </si>
-  <si>
-    <t>03861632600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDD14B</t>
-  </si>
-  <si>
-    <t>03869716500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC97D4</t>
-  </si>
-  <si>
-    <t>03430511100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBDC37</t>
-  </si>
-  <si>
-    <t>03433072200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL879F5</t>
-  </si>
-  <si>
-    <t>03435153300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL31E13</t>
-  </si>
-  <si>
-    <t>2025-10-24</t>
-  </si>
-  <si>
-    <t>03061413100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL34090</t>
-  </si>
-  <si>
-    <t>03062176200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6F1C2</t>
-  </si>
-  <si>
-    <t>03062817300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL79CC2</t>
-  </si>
-  <si>
-    <t>03296863200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLFC0B5</t>
-  </si>
-  <si>
-    <t>03303849200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL54FB6</t>
-  </si>
-  <si>
-    <t>03305786400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2E9C9</t>
-  </si>
-  <si>
-    <t>03943437000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8FCC7</t>
-  </si>
-  <si>
-    <t>03945304200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL117FA</t>
-  </si>
-  <si>
-    <t>03947129500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL794FE</t>
-  </si>
-  <si>
-    <t>2025-10-27</t>
-  </si>
-  <si>
-    <t>03617677000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL06741</t>
-  </si>
-  <si>
-    <t>03618742600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLCA9E3</t>
-  </si>
-  <si>
-    <t>03619621100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB27B6</t>
-  </si>
-  <si>
-    <t>2025-10-28</t>
-  </si>
-  <si>
-    <t>03859356900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2703F</t>
-  </si>
-  <si>
-    <t>03860955600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2ADFF</t>
-  </si>
-  <si>
-    <t>03862320700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD0B1E</t>
-  </si>
-  <si>
-    <t>03032550300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLFB8A5</t>
-  </si>
-  <si>
-    <t>03033750100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF1935</t>
-  </si>
-  <si>
-    <t>03034949200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDFD10</t>
-  </si>
-  <si>
-    <t>03704598000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA5F4C</t>
-  </si>
-  <si>
-    <t>03705694900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEF54F</t>
-  </si>
-  <si>
-    <t>03706625700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6C85C</t>
-  </si>
-  <si>
-    <t>03836523200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL73F84</t>
-  </si>
-  <si>
-    <t>03837078500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF7DA2</t>
-  </si>
-  <si>
-    <t>03837899000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3BB5F</t>
-  </si>
-  <si>
-    <t>03069727300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8EFBA</t>
-  </si>
-  <si>
-    <t>03072196100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL0DC38</t>
-  </si>
-  <si>
-    <t>03073785000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL37109</t>
-  </si>
-  <si>
-    <t>03530365000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL87166</t>
-  </si>
-  <si>
-    <t>03531985900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL06AED</t>
-  </si>
-  <si>
-    <t>03533771200</t>
+    <t>2025-11-11</t>
+  </si>
+  <si>
+    <t>Advance Tax Exemption*</t>
+  </si>
+  <si>
+    <t>03170797600</t>
+  </si>
+  <si>
+    <t>03174944100</t>
+  </si>
+  <si>
+    <t>03178519500</t>
+  </si>
+  <si>
+    <t>AUTO_OUT9B477</t>
+  </si>
+  <si>
+    <t>AUTO_OUTDA6C7</t>
+  </si>
+  <si>
+    <t>AUTO_OUL481A8</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL36AEB</t>
+  </si>
+  <si>
+    <t>03838121300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF8BA3</t>
+  </si>
+  <si>
+    <t>03842688100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9C862</t>
+  </si>
+  <si>
+    <t>03846252900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4E899</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>03507616900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2DFC4</t>
+  </si>
+  <si>
+    <t>03509143000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL08EB6</t>
+  </si>
+  <si>
+    <t>03510295900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1B291</t>
+  </si>
+  <si>
+    <t>03849573800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL08176</t>
+  </si>
+  <si>
+    <t>03854412900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAD7E5</t>
+  </si>
+  <si>
+    <t>03859114200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDEE9A</t>
+  </si>
+  <si>
+    <t>03553032900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD75A3</t>
+  </si>
+  <si>
+    <t>03556012500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL52DD5</t>
+  </si>
+  <si>
+    <t>03558411900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7AABD</t>
+  </si>
+  <si>
+    <t>2025-11-14</t>
+  </si>
+  <si>
+    <t>03574469400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAA347</t>
+  </si>
+  <si>
+    <t>03575171500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2748E</t>
+  </si>
+  <si>
+    <t>03575777400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL552F3</t>
+  </si>
+  <si>
+    <t>03913429300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF5AA6</t>
+  </si>
+  <si>
+    <t>03914446900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL48496</t>
+  </si>
+  <si>
+    <t>03915470600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDD482</t>
+  </si>
+  <si>
+    <t>03247825800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3A243</t>
+  </si>
+  <si>
+    <t>03248657700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE9E04</t>
+  </si>
+  <si>
+    <t>03249336500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB91BA</t>
+  </si>
+  <si>
+    <t>03393321400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEDE5E</t>
+  </si>
+  <si>
+    <t>03394569000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL78E06</t>
+  </si>
+  <si>
+    <t>03395283600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL451F4</t>
+  </si>
+  <si>
+    <t>2025-11-18</t>
+  </si>
+  <si>
+    <t>03109513500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEA405</t>
+  </si>
+  <si>
+    <t>03110784900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBD011</t>
+  </si>
+  <si>
+    <t>03112514600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCDC15</t>
+  </si>
+  <si>
+    <t>03627628600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB000D</t>
+  </si>
+  <si>
+    <t>03630149300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL671A7</t>
+  </si>
+  <si>
+    <t>03632015300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL944F5</t>
+  </si>
+  <si>
+    <t>03955331500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL06962</t>
+  </si>
+  <si>
+    <t>03957561200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2E325</t>
+  </si>
+  <si>
+    <t>03959693900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3E724</t>
+  </si>
+  <si>
+    <t>03472307000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3C6E7</t>
+  </si>
+  <si>
+    <t>03474555600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL592CA</t>
+  </si>
+  <si>
+    <t>03476046200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL676B6</t>
+  </si>
+  <si>
+    <t>03298894600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD56CF</t>
+  </si>
+  <si>
+    <t>03299631400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7668C</t>
+  </si>
+  <si>
+    <t>03300068900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA8F57</t>
+  </si>
+  <si>
+    <t>2025-11-19</t>
+  </si>
+  <si>
+    <t>03608297000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2F37A</t>
+  </si>
+  <si>
+    <t>03608824900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL02596</t>
+  </si>
+  <si>
+    <t>03609276500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB5767</t>
+  </si>
+  <si>
+    <t>03158988100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8FCD3</t>
+  </si>
+  <si>
+    <t>03159491300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC5B68</t>
+  </si>
+  <si>
+    <t>03159981500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLED6FF</t>
+  </si>
+  <si>
+    <t>03866500900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1CFDB</t>
+  </si>
+  <si>
+    <t>03867365900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA36A3</t>
+  </si>
+  <si>
+    <t>03868160000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL124EC</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>03029759600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7DBBE</t>
+  </si>
+  <si>
+    <t>03031130300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL025A0</t>
+  </si>
+  <si>
+    <t>03031803900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDD2A2</t>
+  </si>
+  <si>
+    <t>03308284800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFC67B</t>
+  </si>
+  <si>
+    <t>03309114800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF7793</t>
+  </si>
+  <si>
+    <t>03309877800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEE034</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>03197327200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFD494</t>
+  </si>
+  <si>
+    <t>03200810700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDFD85</t>
+  </si>
+  <si>
+    <t>03203079700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE515E</t>
+  </si>
+  <si>
+    <t>2025-11-25</t>
+  </si>
+  <si>
+    <t>03384833700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4944D</t>
+  </si>
+  <si>
+    <t>03388589500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL87DFA</t>
+  </si>
+  <si>
+    <t>03399606500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF7F7F</t>
+  </si>
+  <si>
+    <t>2025-11-26</t>
+  </si>
+  <si>
+    <t>03913027000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL03E06</t>
+  </si>
+  <si>
+    <t>03914851300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL83A87</t>
+  </si>
+  <si>
+    <t>03917276200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5DC68</t>
+  </si>
+  <si>
+    <t>03306086700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBE6EB</t>
+  </si>
+  <si>
+    <t>03307502300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE1E8D</t>
+  </si>
+  <si>
+    <t>03308953100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6D75D</t>
+  </si>
+  <si>
+    <t>03820889500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1E547</t>
+  </si>
+  <si>
+    <t>03824014600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8A6BD</t>
+  </si>
+  <si>
+    <t>03826038300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC7FB6</t>
+  </si>
+  <si>
+    <t>03844974400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1CCFC</t>
+  </si>
+  <si>
+    <t>03849481700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBC625</t>
+  </si>
+  <si>
+    <t>03851508000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL091C9</t>
+  </si>
+  <si>
+    <t>03623322900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL19E4D</t>
+  </si>
+  <si>
+    <t>03626219400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL97EF9</t>
+  </si>
+  <si>
+    <t>03628722400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL113FA</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>03751232200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4BB72</t>
+  </si>
+  <si>
+    <t>03753324500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6557C</t>
+  </si>
+  <si>
+    <t>03755432100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3A830</t>
+  </si>
+  <si>
+    <t>03323510500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3FAD0</t>
+  </si>
+  <si>
+    <t>03325716300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL876E2</t>
+  </si>
+  <si>
+    <t>03327671400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC1B1A</t>
+  </si>
+  <si>
+    <t>03514958400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL52132</t>
+  </si>
+  <si>
+    <t>03516871500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCC1D6</t>
+  </si>
+  <si>
+    <t>03518746600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9A078</t>
+  </si>
+  <si>
+    <t>03105815500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDE157</t>
+  </si>
+  <si>
+    <t>03108492300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0E325</t>
+  </si>
+  <si>
+    <t>03110133900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0A00F</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>03748992100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0352D</t>
+  </si>
+  <si>
+    <t>03760459900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9480D</t>
+  </si>
+  <si>
+    <t>03763592100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF967A</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>03596696800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFCD90</t>
+  </si>
+  <si>
+    <t>03601150400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB4FE3</t>
+  </si>
+  <si>
+    <t>03603779500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5867F</t>
+  </si>
+  <si>
+    <t>03829877400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9760D</t>
+  </si>
+  <si>
+    <t>03833479500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD236A</t>
+  </si>
+  <si>
+    <t>03838645800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3CC27</t>
+  </si>
+  <si>
+    <t>03813441800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL68BD8</t>
+  </si>
+  <si>
+    <t>03820363800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3C8CF</t>
+  </si>
+  <si>
+    <t>03822210400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL69EA6</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>03847230300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD4A59</t>
+  </si>
+  <si>
+    <t>03849063900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL35C2E</t>
+  </si>
+  <si>
+    <t>03850533000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2DAF4</t>
+  </si>
+  <si>
+    <t>03173774600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLACB45</t>
+  </si>
+  <si>
+    <t>03175527300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB9616</t>
+  </si>
+  <si>
+    <t>03176867700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL14549</t>
+  </si>
+  <si>
+    <t>03312160500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL094B6</t>
+  </si>
+  <si>
+    <t>03314025500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL39464</t>
+  </si>
+  <si>
+    <t>03315431600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL14B01</t>
+  </si>
+  <si>
+    <t>03126642300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2BC6C</t>
+  </si>
+  <si>
+    <t>03129224000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL27987</t>
+  </si>
+  <si>
+    <t>03130628300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3E1B5</t>
+  </si>
+  <si>
+    <t>03923984600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL46834</t>
+  </si>
+  <si>
+    <t>03926140100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5132B</t>
+  </si>
+  <si>
+    <t>03928107500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC47A8</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>03619295800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5261E</t>
+  </si>
+  <si>
+    <t>03621488400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCE6FD</t>
+  </si>
+  <si>
+    <t>03623525400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBD23E</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>03629843500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC8DE5</t>
+  </si>
+  <si>
+    <t>03632092900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL51916</t>
+  </si>
+  <si>
+    <t>03634240800</t>
   </si>
 </sst>
 </file>
@@ -711,7 +1200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -719,7 +1208,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1000,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BO4"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="10.7265625"/>
@@ -1012,8 +1500,7 @@
     <col min="7" max="7" customWidth="true" style="1" width="12.453125"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="17.26953125"/>
     <col min="9" max="9" customWidth="true" style="1" width="26.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="3" width="10.0"/>
-    <col min="11" max="11" customWidth="true" style="3" width="11.90625"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="3" width="23.6328125"/>
     <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.453125"/>
     <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="10.54296875"/>
     <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="14.36328125"/>
@@ -1068,9 +1555,10 @@
     <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="11.1796875"/>
     <col min="65" max="66" bestFit="true" customWidth="true" style="3" width="22.6328125"/>
     <col min="67" max="67" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" width="23.453125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1272,10 +1760,13 @@
       <c r="BO1" t="s" s="0">
         <v>66</v>
       </c>
+      <c r="BP1" t="s" s="0">
+        <v>120</v>
+      </c>
     </row>
-    <row r="2" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>374</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>91</v>
@@ -1293,13 +1784,13 @@
         <v>69</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J2" s="2">
-        <v>3</v>
-      </c>
-      <c r="K2" s="7" t="n">
-        <v>24.452440352577252</v>
+        <v>93</v>
+      </c>
+      <c r="J2" s="3">
+        <v>24.438292084300599</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>24.630439882760527</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>68</v>
@@ -1317,16 +1808,16 @@
         <v>72</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>73</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="U2" t="s" s="0">
         <v>73</v>
@@ -1347,10 +1838,10 @@
         <v>73</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AC2" s="2">
         <v>1</v>
@@ -1359,19 +1850,19 @@
         <v>75</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="AG2" t="s" s="0">
         <v>75</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AJ2" t="s" s="0">
         <v>73</v>
@@ -1416,7 +1907,7 @@
         <v>86</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="AY2" s="1" t="s">
         <v>87</v>
@@ -1431,28 +1922,28 @@
         <v>89</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="BD2" s="1" t="s">
         <v>90</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>213</v>
+        <v>376</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="BI2" s="5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="BK2" s="1" t="s">
         <v>68</v>
@@ -1469,10 +1960,13 @@
       <c r="BO2" t="s" s="0">
         <v>73</v>
       </c>
+      <c r="BP2" t="s" s="0">
+        <v>75</v>
+      </c>
     </row>
-    <row r="3" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>377</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>91</v>
@@ -1490,13 +1984,13 @@
         <v>69</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J3" s="2">
-        <v>3</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>24.696517640543398</v>
+        <v>93</v>
+      </c>
+      <c r="J3" s="3">
+        <v>24.438292084300599</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>24.30312902295062</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>68</v>
@@ -1514,16 +2008,16 @@
         <v>72</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>73</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="U3" t="s" s="0">
         <v>73</v>
@@ -1544,10 +2038,10 @@
         <v>73</v>
       </c>
       <c r="AA3" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AC3" s="2">
         <v>1</v>
@@ -1556,19 +2050,19 @@
         <v>75</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s" s="0">
         <v>75</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AJ3" t="s" s="0">
         <v>73</v>
@@ -1613,7 +2107,7 @@
         <v>86</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="AY3" s="1" t="s">
         <v>87</v>
@@ -1628,28 +2122,28 @@
         <v>89</v>
       </c>
       <c r="BC3" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BD3" s="1" t="s">
         <v>90</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>215</v>
+        <v>378</v>
       </c>
       <c r="BF3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BI3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BI3" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="BK3" s="1" t="s">
         <v>68</v>
@@ -1666,10 +2160,13 @@
       <c r="BO3" t="s" s="0">
         <v>75</v>
       </c>
+      <c r="BP3" t="s" s="0">
+        <v>73</v>
+      </c>
     </row>
-    <row r="4" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>379</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>91</v>
@@ -1687,13 +2184,13 @@
         <v>69</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J4" s="2">
-        <v>3</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>24.29227926333177</v>
+        <v>93</v>
+      </c>
+      <c r="J4" s="3">
+        <v>24.438292084300599</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>24.201839236788263</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>68</v>
@@ -1711,16 +2208,16 @@
         <v>72</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>75</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="U4" t="s" s="0">
         <v>73</v>
@@ -1741,10 +2238,10 @@
         <v>73</v>
       </c>
       <c r="AA4" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AC4" s="2">
         <v>1</v>
@@ -1753,19 +2250,19 @@
         <v>75</v>
       </c>
       <c r="AE4" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="0">
         <v>75</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="AJ4" t="s" s="0">
         <v>73</v>
@@ -1810,7 +2307,7 @@
         <v>86</v>
       </c>
       <c r="AX4" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="AY4" s="1" t="s">
         <v>87</v>
@@ -1825,28 +2322,28 @@
         <v>89</v>
       </c>
       <c r="BC4" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BD4" s="1" t="s">
         <v>90</v>
       </c>
       <c r="BE4" s="1" t="s">
-        <v>217</v>
+        <v>380</v>
       </c>
       <c r="BF4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BG4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BI4" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="BJ4" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="BG4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="BH4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BI4" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="BJ4" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="BK4" s="1" t="s">
         <v>68</v>
@@ -1862,6 +2359,9 @@
       </c>
       <c r="BO4" t="s" s="0">
         <v>73</v>
+      </c>
+      <c r="BP4" t="s" s="0">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="419">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -1162,6 +1162,120 @@
   </si>
   <si>
     <t>03634240800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL606A9</t>
+  </si>
+  <si>
+    <t>2025-12-16</t>
+  </si>
+  <si>
+    <t>03992144400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2FB12</t>
+  </si>
+  <si>
+    <t>03994225700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBAF21</t>
+  </si>
+  <si>
+    <t>03996839500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD9C94</t>
+  </si>
+  <si>
+    <t>03363245900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2BBFB</t>
+  </si>
+  <si>
+    <t>03366242400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5D74C</t>
+  </si>
+  <si>
+    <t>03367638300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6B06C</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>03019837600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL08112</t>
+  </si>
+  <si>
+    <t>03023974600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL35C40</t>
+  </si>
+  <si>
+    <t>03026327700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9A391</t>
+  </si>
+  <si>
+    <t>03115335000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL46F66</t>
+  </si>
+  <si>
+    <t>03118922400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL01FD4</t>
+  </si>
+  <si>
+    <t>03121529100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8C342</t>
+  </si>
+  <si>
+    <t>03530853200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD1C60</t>
+  </si>
+  <si>
+    <t>03533514000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL55261</t>
+  </si>
+  <si>
+    <t>03535753000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL981C2</t>
+  </si>
+  <si>
+    <t>03163286200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5AAC5</t>
+  </si>
+  <si>
+    <t>03163941200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0CE11</t>
+  </si>
+  <si>
+    <t>03164497600</t>
   </si>
 </sst>
 </file>
@@ -1766,7 +1880,7 @@
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>91</v>
@@ -1790,7 +1904,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>24.630439882760527</v>
+        <v>24.26546403670583</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>68</v>
@@ -1808,7 +1922,7 @@
         <v>72</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>94</v>
@@ -1817,7 +1931,7 @@
         <v>73</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="U2" t="s" s="0">
         <v>73</v>
@@ -1928,7 +2042,7 @@
         <v>90</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="BF2" s="1" t="s">
         <v>92</v>
@@ -1966,7 +2080,7 @@
     </row>
     <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>91</v>
@@ -1990,7 +2104,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>24.30312902295062</v>
+        <v>24.779249826889846</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>68</v>
@@ -2008,7 +2122,7 @@
         <v>72</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>94</v>
@@ -2017,7 +2131,7 @@
         <v>73</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="U3" t="s" s="0">
         <v>73</v>
@@ -2128,7 +2242,7 @@
         <v>90</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="BF3" s="1" t="s">
         <v>111</v>
@@ -2166,7 +2280,7 @@
     </row>
     <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>91</v>
@@ -2190,7 +2304,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>24.201839236788263</v>
+        <v>24.042029992962327</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>68</v>
@@ -2208,7 +2322,7 @@
         <v>72</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>94</v>
@@ -2217,7 +2331,7 @@
         <v>75</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="U4" t="s" s="0">
         <v>73</v>
@@ -2328,7 +2442,7 @@
         <v>90</v>
       </c>
       <c r="BE4" s="1" t="s">
-        <v>380</v>
+        <v>418</v>
       </c>
       <c r="BF4" s="1" t="s">
         <v>112</v>

--- a/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="438">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -1276,6 +1276,63 @@
   </si>
   <si>
     <t>03164497600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC0D0B</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>03385378900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL28DB2</t>
+  </si>
+  <si>
+    <t>03386158600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL33031</t>
+  </si>
+  <si>
+    <t>03387138500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF2241</t>
+  </si>
+  <si>
+    <t>03053401800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE3DAF</t>
+  </si>
+  <si>
+    <t>03054363300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0FB45</t>
+  </si>
+  <si>
+    <t>03055045800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL62304</t>
+  </si>
+  <si>
+    <t>03769222400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8E23A</t>
+  </si>
+  <si>
+    <t>03769950400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC2216</t>
+  </si>
+  <si>
+    <t>03770717900</t>
   </si>
 </sst>
 </file>
@@ -1880,7 +1937,7 @@
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>91</v>
@@ -1904,7 +1961,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>24.26546403670583</v>
+        <v>24.693290198649297</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>68</v>
@@ -1922,7 +1979,7 @@
         <v>72</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>94</v>
@@ -1931,7 +1988,7 @@
         <v>73</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="U2" t="s" s="0">
         <v>73</v>
@@ -2042,7 +2099,7 @@
         <v>90</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="BF2" s="1" t="s">
         <v>92</v>
@@ -2080,7 +2137,7 @@
     </row>
     <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>91</v>
@@ -2104,7 +2161,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>24.779249826889846</v>
+        <v>24.98373552152846</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>68</v>
@@ -2122,7 +2179,7 @@
         <v>72</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>94</v>
@@ -2131,7 +2188,7 @@
         <v>73</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="U3" t="s" s="0">
         <v>73</v>
@@ -2242,7 +2299,7 @@
         <v>90</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="BF3" s="1" t="s">
         <v>111</v>
@@ -2280,7 +2337,7 @@
     </row>
     <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>91</v>
@@ -2304,7 +2361,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>24.042029992962327</v>
+        <v>24.034612187009028</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>68</v>
@@ -2322,7 +2379,7 @@
         <v>72</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>94</v>
@@ -2331,7 +2388,7 @@
         <v>75</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="U4" t="s" s="0">
         <v>73</v>
@@ -2442,7 +2499,7 @@
         <v>90</v>
       </c>
       <c r="BE4" s="1" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="BF4" s="1" t="s">
         <v>112</v>

--- a/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="132">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -300,9 +300,6 @@
     <t>03004121400</t>
   </si>
   <si>
-    <t>N02N02N02N02N02N02</t>
-  </si>
-  <si>
     <t>Selenium</t>
   </si>
   <si>
@@ -360,15 +357,6 @@
     <t>03004121402</t>
   </si>
   <si>
-    <t>42101-10714113-4</t>
-  </si>
-  <si>
-    <t>42101-10714113-5</t>
-  </si>
-  <si>
-    <t>42101-10714113-6</t>
-  </si>
-  <si>
     <t>12321</t>
   </si>
   <si>
@@ -378,961 +366,55 @@
     <t>12323</t>
   </si>
   <si>
-    <t>2025-11-11</t>
-  </si>
-  <si>
     <t>Advance Tax Exemption*</t>
   </si>
   <si>
-    <t>03170797600</t>
-  </si>
-  <si>
-    <t>03174944100</t>
-  </si>
-  <si>
-    <t>03178519500</t>
-  </si>
-  <si>
-    <t>AUTO_OUT9B477</t>
-  </si>
-  <si>
-    <t>AUTO_OUTDA6C7</t>
-  </si>
-  <si>
-    <t>AUTO_OUL481A8</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL36AEB</t>
-  </si>
-  <si>
-    <t>03838121300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF8BA3</t>
-  </si>
-  <si>
-    <t>03842688100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL9C862</t>
-  </si>
-  <si>
-    <t>03846252900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4E899</t>
-  </si>
-  <si>
-    <t>2025-11-12</t>
-  </si>
-  <si>
-    <t>03507616900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2DFC4</t>
-  </si>
-  <si>
-    <t>03509143000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL08EB6</t>
-  </si>
-  <si>
-    <t>03510295900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1B291</t>
-  </si>
-  <si>
-    <t>03849573800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL08176</t>
-  </si>
-  <si>
-    <t>03854412900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLAD7E5</t>
-  </si>
-  <si>
-    <t>03859114200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDEE9A</t>
-  </si>
-  <si>
-    <t>03553032900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD75A3</t>
-  </si>
-  <si>
-    <t>03556012500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL52DD5</t>
-  </si>
-  <si>
-    <t>03558411900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL7AABD</t>
-  </si>
-  <si>
-    <t>2025-11-14</t>
-  </si>
-  <si>
-    <t>03574469400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLAA347</t>
-  </si>
-  <si>
-    <t>03575171500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2748E</t>
-  </si>
-  <si>
-    <t>03575777400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL552F3</t>
-  </si>
-  <si>
-    <t>03913429300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF5AA6</t>
-  </si>
-  <si>
-    <t>03914446900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL48496</t>
-  </si>
-  <si>
-    <t>03915470600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDD482</t>
-  </si>
-  <si>
-    <t>03247825800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3A243</t>
-  </si>
-  <si>
-    <t>03248657700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE9E04</t>
-  </si>
-  <si>
-    <t>03249336500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB91BA</t>
-  </si>
-  <si>
-    <t>03393321400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEDE5E</t>
-  </si>
-  <si>
-    <t>03394569000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL78E06</t>
-  </si>
-  <si>
-    <t>03395283600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL451F4</t>
-  </si>
-  <si>
-    <t>2025-11-18</t>
-  </si>
-  <si>
-    <t>03109513500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEA405</t>
-  </si>
-  <si>
-    <t>03110784900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBD011</t>
-  </si>
-  <si>
-    <t>03112514600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLCDC15</t>
-  </si>
-  <si>
-    <t>03627628600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB000D</t>
-  </si>
-  <si>
-    <t>03630149300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL671A7</t>
-  </si>
-  <si>
-    <t>03632015300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL944F5</t>
-  </si>
-  <si>
-    <t>03955331500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL06962</t>
-  </si>
-  <si>
-    <t>03957561200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2E325</t>
-  </si>
-  <si>
-    <t>03959693900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3E724</t>
-  </si>
-  <si>
-    <t>03472307000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3C6E7</t>
-  </si>
-  <si>
-    <t>03474555600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL592CA</t>
-  </si>
-  <si>
-    <t>03476046200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL676B6</t>
-  </si>
-  <si>
-    <t>03298894600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD56CF</t>
-  </si>
-  <si>
-    <t>03299631400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL7668C</t>
-  </si>
-  <si>
-    <t>03300068900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA8F57</t>
-  </si>
-  <si>
-    <t>2025-11-19</t>
-  </si>
-  <si>
-    <t>03608297000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2F37A</t>
-  </si>
-  <si>
-    <t>03608824900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL02596</t>
-  </si>
-  <si>
-    <t>03609276500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB5767</t>
-  </si>
-  <si>
-    <t>03158988100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8FCD3</t>
-  </si>
-  <si>
-    <t>03159491300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC5B68</t>
-  </si>
-  <si>
-    <t>03159981500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLED6FF</t>
-  </si>
-  <si>
-    <t>03866500900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1CFDB</t>
-  </si>
-  <si>
-    <t>03867365900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLA36A3</t>
-  </si>
-  <si>
-    <t>03868160000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL124EC</t>
-  </si>
-  <si>
-    <t>2025-11-20</t>
-  </si>
-  <si>
-    <t>03029759600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL7DBBE</t>
-  </si>
-  <si>
-    <t>03031130300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL025A0</t>
-  </si>
-  <si>
-    <t>03031803900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDD2A2</t>
-  </si>
-  <si>
-    <t>03308284800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLFC67B</t>
-  </si>
-  <si>
-    <t>03309114800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF7793</t>
-  </si>
-  <si>
-    <t>03309877800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLEE034</t>
-  </si>
-  <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
-    <t>03197327200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLFD494</t>
-  </si>
-  <si>
-    <t>03200810700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDFD85</t>
-  </si>
-  <si>
-    <t>03203079700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE515E</t>
-  </si>
-  <si>
-    <t>2025-11-25</t>
-  </si>
-  <si>
-    <t>03384833700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4944D</t>
-  </si>
-  <si>
-    <t>03388589500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL87DFA</t>
-  </si>
-  <si>
-    <t>03399606500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF7F7F</t>
-  </si>
-  <si>
-    <t>2025-11-26</t>
-  </si>
-  <si>
-    <t>03913027000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL03E06</t>
-  </si>
-  <si>
-    <t>03914851300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL83A87</t>
-  </si>
-  <si>
-    <t>03917276200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5DC68</t>
-  </si>
-  <si>
-    <t>03306086700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBE6EB</t>
-  </si>
-  <si>
-    <t>03307502300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE1E8D</t>
-  </si>
-  <si>
-    <t>03308953100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6D75D</t>
-  </si>
-  <si>
-    <t>03820889500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1E547</t>
-  </si>
-  <si>
-    <t>03824014600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8A6BD</t>
-  </si>
-  <si>
-    <t>03826038300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC7FB6</t>
-  </si>
-  <si>
-    <t>03844974400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1CCFC</t>
-  </si>
-  <si>
-    <t>03849481700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBC625</t>
-  </si>
-  <si>
-    <t>03851508000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL091C9</t>
-  </si>
-  <si>
-    <t>03623322900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL19E4D</t>
-  </si>
-  <si>
-    <t>03626219400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL97EF9</t>
-  </si>
-  <si>
-    <t>03628722400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL113FA</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>03751232200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL4BB72</t>
-  </si>
-  <si>
-    <t>03753324500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6557C</t>
-  </si>
-  <si>
-    <t>03755432100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3A830</t>
-  </si>
-  <si>
-    <t>03323510500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3FAD0</t>
-  </si>
-  <si>
-    <t>03325716300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL876E2</t>
-  </si>
-  <si>
-    <t>03327671400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC1B1A</t>
-  </si>
-  <si>
-    <t>03514958400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL52132</t>
-  </si>
-  <si>
-    <t>03516871500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLCC1D6</t>
-  </si>
-  <si>
-    <t>03518746600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL9A078</t>
-  </si>
-  <si>
-    <t>03105815500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLDE157</t>
-  </si>
-  <si>
-    <t>03108492300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL0E325</t>
-  </si>
-  <si>
-    <t>03110133900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL0A00F</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>03748992100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL0352D</t>
-  </si>
-  <si>
-    <t>03760459900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL9480D</t>
-  </si>
-  <si>
-    <t>03763592100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF967A</t>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
-    <t>03596696800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLFCD90</t>
-  </si>
-  <si>
-    <t>03601150400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB4FE3</t>
-  </si>
-  <si>
-    <t>03603779500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5867F</t>
-  </si>
-  <si>
-    <t>03829877400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL9760D</t>
-  </si>
-  <si>
-    <t>03833479500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD236A</t>
-  </si>
-  <si>
-    <t>03838645800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3CC27</t>
-  </si>
-  <si>
-    <t>03813441800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL68BD8</t>
-  </si>
-  <si>
-    <t>03820363800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3C8CF</t>
-  </si>
-  <si>
-    <t>03822210400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL69EA6</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>03847230300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD4A59</t>
-  </si>
-  <si>
-    <t>03849063900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL35C2E</t>
-  </si>
-  <si>
-    <t>03850533000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2DAF4</t>
-  </si>
-  <si>
-    <t>03173774600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLACB45</t>
-  </si>
-  <si>
-    <t>03175527300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB9616</t>
-  </si>
-  <si>
-    <t>03176867700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL14549</t>
-  </si>
-  <si>
-    <t>03312160500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL094B6</t>
-  </si>
-  <si>
-    <t>03314025500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL39464</t>
-  </si>
-  <si>
-    <t>03315431600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL14B01</t>
-  </si>
-  <si>
-    <t>03126642300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2BC6C</t>
-  </si>
-  <si>
-    <t>03129224000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL27987</t>
-  </si>
-  <si>
-    <t>03130628300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3E1B5</t>
-  </si>
-  <si>
-    <t>03923984600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL46834</t>
-  </si>
-  <si>
-    <t>03926140100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5132B</t>
-  </si>
-  <si>
-    <t>03928107500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC47A8</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>03619295800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5261E</t>
-  </si>
-  <si>
-    <t>03621488400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLCE6FD</t>
-  </si>
-  <si>
-    <t>03623525400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBD23E</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>03629843500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC8DE5</t>
-  </si>
-  <si>
-    <t>03632092900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL51916</t>
-  </si>
-  <si>
-    <t>03634240800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL606A9</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t>03992144400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2FB12</t>
-  </si>
-  <si>
-    <t>03994225700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBAF21</t>
-  </si>
-  <si>
-    <t>03996839500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD9C94</t>
-  </si>
-  <si>
-    <t>03363245900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL2BBFB</t>
-  </si>
-  <si>
-    <t>03366242400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5D74C</t>
-  </si>
-  <si>
-    <t>03367638300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6B06C</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>03019837600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL08112</t>
-  </si>
-  <si>
-    <t>03023974600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL35C40</t>
-  </si>
-  <si>
-    <t>03026327700</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL9A391</t>
-  </si>
-  <si>
-    <t>03115335000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL46F66</t>
-  </si>
-  <si>
-    <t>03118922400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL01FD4</t>
-  </si>
-  <si>
-    <t>03121529100</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8C342</t>
-  </si>
-  <si>
-    <t>03530853200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD1C60</t>
-  </si>
-  <si>
-    <t>03533514000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL55261</t>
-  </si>
-  <si>
-    <t>03535753000</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL981C2</t>
-  </si>
-  <si>
-    <t>03163286200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL5AAC5</t>
-  </si>
-  <si>
-    <t>03163941200</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL0CE11</t>
-  </si>
-  <si>
-    <t>03164497600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC0D0B</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>03385378900</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL28DB2</t>
-  </si>
-  <si>
-    <t>03386158600</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL33031</t>
-  </si>
-  <si>
-    <t>03387138500</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLF2241</t>
-  </si>
-  <si>
-    <t>03053401800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLE3DAF</t>
-  </si>
-  <si>
-    <t>03054363300</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL0FB45</t>
-  </si>
-  <si>
-    <t>03055045800</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL62304</t>
-  </si>
-  <si>
-    <t>03769222400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8E23A</t>
-  </si>
-  <si>
-    <t>03769950400</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC2216</t>
-  </si>
-  <si>
-    <t>03770717900</t>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFF84D</t>
+  </si>
+  <si>
+    <t>03928278300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0DF67</t>
+  </si>
+  <si>
+    <t>03929426800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE9CDA</t>
+  </si>
+  <si>
+    <t>03930466300</t>
+  </si>
+  <si>
+    <t>4210110714113</t>
+  </si>
+  <si>
+    <t>001001002004018059UTK001</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL57BC1</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>03534494500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFD780</t>
+  </si>
+  <si>
+    <t>03537049000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC01A8</t>
+  </si>
+  <si>
+    <t>03538348600</t>
   </si>
 </sst>
 </file>
@@ -1932,12 +1014,12 @@
         <v>66</v>
       </c>
       <c r="BP1" t="s" s="0">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>432</v>
+        <v>125</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>91</v>
@@ -1955,13 +1037,13 @@
         <v>69</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="J2" s="3">
         <v>24.438292084300599</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>24.693290198649297</v>
+        <v>24.450068312795135</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>68</v>
@@ -1979,16 +1061,16 @@
         <v>72</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>420</v>
+        <v>126</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>73</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>420</v>
+        <v>126</v>
       </c>
       <c r="U2" t="s" s="0">
         <v>73</v>
@@ -2009,10 +1091,10 @@
         <v>73</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AC2" s="2">
         <v>1</v>
@@ -2021,19 +1103,19 @@
         <v>75</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG2" t="s" s="0">
         <v>75</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AJ2" t="s" s="0">
         <v>73</v>
@@ -2078,7 +1160,7 @@
         <v>86</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AY2" s="1" t="s">
         <v>87</v>
@@ -2093,13 +1175,13 @@
         <v>89</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="BD2" s="1" t="s">
         <v>90</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>433</v>
+        <v>127</v>
       </c>
       <c r="BF2" s="1" t="s">
         <v>92</v>
@@ -2111,10 +1193,10 @@
         <v>92</v>
       </c>
       <c r="BI2" s="5" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="BK2" s="1" t="s">
         <v>68</v>
@@ -2137,7 +1219,7 @@
     </row>
     <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>434</v>
+        <v>128</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>91</v>
@@ -2155,13 +1237,13 @@
         <v>69</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="J3" s="3">
         <v>24.438292084300599</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>24.98373552152846</v>
+        <v>24.58441806644632</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>68</v>
@@ -2179,16 +1261,16 @@
         <v>72</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>420</v>
+        <v>126</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>73</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>420</v>
+        <v>126</v>
       </c>
       <c r="U3" t="s" s="0">
         <v>73</v>
@@ -2209,10 +1291,10 @@
         <v>73</v>
       </c>
       <c r="AA3" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AC3" s="2">
         <v>1</v>
@@ -2221,19 +1303,19 @@
         <v>75</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="0">
         <v>75</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AJ3" t="s" s="0">
         <v>73</v>
@@ -2278,7 +1360,7 @@
         <v>86</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AY3" s="1" t="s">
         <v>87</v>
@@ -2293,28 +1375,28 @@
         <v>89</v>
       </c>
       <c r="BC3" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BD3" s="1" t="s">
         <v>90</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>435</v>
+        <v>129</v>
       </c>
       <c r="BF3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BG3" s="1" t="s">
         <v>92</v>
       </c>
       <c r="BH3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BI3" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="BJ3" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="BK3" s="1" t="s">
         <v>68</v>
@@ -2337,7 +1419,7 @@
     </row>
     <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>436</v>
+        <v>130</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>91</v>
@@ -2355,13 +1437,13 @@
         <v>69</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="J4" s="3">
         <v>24.438292084300599</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>24.034612187009028</v>
+        <v>24.207824306307835</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>68</v>
@@ -2379,16 +1461,16 @@
         <v>72</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>420</v>
+        <v>126</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>75</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>420</v>
+        <v>126</v>
       </c>
       <c r="U4" t="s" s="0">
         <v>73</v>
@@ -2409,10 +1491,10 @@
         <v>73</v>
       </c>
       <c r="AA4" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AC4" s="2">
         <v>1</v>
@@ -2421,19 +1503,19 @@
         <v>75</v>
       </c>
       <c r="AE4" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="s" s="0">
         <v>75</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AJ4" t="s" s="0">
         <v>73</v>
@@ -2478,7 +1560,7 @@
         <v>86</v>
       </c>
       <c r="AX4" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AY4" s="1" t="s">
         <v>87</v>
@@ -2493,28 +1575,28 @@
         <v>89</v>
       </c>
       <c r="BC4" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BD4" s="1" t="s">
         <v>90</v>
       </c>
       <c r="BE4" s="1" t="s">
-        <v>437</v>
+        <v>131</v>
       </c>
       <c r="BF4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BG4" s="1" t="s">
         <v>92</v>
       </c>
       <c r="BH4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BI4" s="5" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="BJ4" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="BK4" s="1" t="s">
         <v>68</v>

--- a/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="269">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -415,6 +415,417 @@
   </si>
   <si>
     <t>03538348600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL329C6</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>03963924900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL70D7E</t>
+  </si>
+  <si>
+    <t>03965659100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL41EC3</t>
+  </si>
+  <si>
+    <t>03970738100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1577F</t>
+  </si>
+  <si>
+    <t>03120894700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDCBC1</t>
+  </si>
+  <si>
+    <t>03122222600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL63A86</t>
+  </si>
+  <si>
+    <t>03123100300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCDDD7</t>
+  </si>
+  <si>
+    <t>03605532500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0384D</t>
+  </si>
+  <si>
+    <t>03606757000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5C57D</t>
+  </si>
+  <si>
+    <t>03607641100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL485AA</t>
+  </si>
+  <si>
+    <t>03878513600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1827B</t>
+  </si>
+  <si>
+    <t>03879459400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCE7E8</t>
+  </si>
+  <si>
+    <t>03880167800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFDE97</t>
+  </si>
+  <si>
+    <t>03289805100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL83843</t>
+  </si>
+  <si>
+    <t>03290733700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCEF2D</t>
+  </si>
+  <si>
+    <t>03291556100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4A8F6</t>
+  </si>
+  <si>
+    <t>03839805100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL13EA7</t>
+  </si>
+  <si>
+    <t>03841322300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDDD13</t>
+  </si>
+  <si>
+    <t>03842096700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1645E</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>03284684800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA9CA6</t>
+  </si>
+  <si>
+    <t>03285658400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL76BE5</t>
+  </si>
+  <si>
+    <t>03286697700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6C464</t>
+  </si>
+  <si>
+    <t>03169080000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL20BDF</t>
+  </si>
+  <si>
+    <t>03169970700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL18F3B</t>
+  </si>
+  <si>
+    <t>03170689400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL38CAD</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>03180551000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL84E8B</t>
+  </si>
+  <si>
+    <t>03181378100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLADF04</t>
+  </si>
+  <si>
+    <t>03182011399</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1225E</t>
+  </si>
+  <si>
+    <t>03003496800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC88F7</t>
+  </si>
+  <si>
+    <t>03004392300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFE1F1</t>
+  </si>
+  <si>
+    <t>03005087000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2DDCB</t>
+  </si>
+  <si>
+    <t>03964047800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFD66F</t>
+  </si>
+  <si>
+    <t>03964877400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL34C51</t>
+  </si>
+  <si>
+    <t>03965566200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL87033</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>03218916500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCFE96</t>
+  </si>
+  <si>
+    <t>03219788300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD49B6</t>
+  </si>
+  <si>
+    <t>03220505600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9BF36</t>
+  </si>
+  <si>
+    <t>03601503100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL16538</t>
+  </si>
+  <si>
+    <t>03602386900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL23F08</t>
+  </si>
+  <si>
+    <t>03603066000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLABDED</t>
+  </si>
+  <si>
+    <t>03028388300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL60F1C</t>
+  </si>
+  <si>
+    <t>03029234900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL446E8</t>
+  </si>
+  <si>
+    <t>03029877800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL86FFF</t>
+  </si>
+  <si>
+    <t>03961020000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL55BEA</t>
+  </si>
+  <si>
+    <t>03961888100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD062B</t>
+  </si>
+  <si>
+    <t>03962554000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL72F96</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>03159262000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9E721</t>
+  </si>
+  <si>
+    <t>03160932000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL327BC</t>
+  </si>
+  <si>
+    <t>03162197900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL84E11</t>
+  </si>
+  <si>
+    <t>03873856300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL57706</t>
+  </si>
+  <si>
+    <t>03875598900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB95CA</t>
+  </si>
+  <si>
+    <t>03877565300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL86F26</t>
+  </si>
+  <si>
+    <t>03735893400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL747AF</t>
+  </si>
+  <si>
+    <t>03737177000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE8A8E</t>
+  </si>
+  <si>
+    <t>03738341300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL81056</t>
+  </si>
+  <si>
+    <t>03151473800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6BECF</t>
+  </si>
+  <si>
+    <t>03152513200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL34D03</t>
+  </si>
+  <si>
+    <t>03153892500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDA58D</t>
+  </si>
+  <si>
+    <t>03558913000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL339DC</t>
+  </si>
+  <si>
+    <t>03575144600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDEB72</t>
+  </si>
+  <si>
+    <t>03578586700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0D1B1</t>
+  </si>
+  <si>
+    <t>03179675600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5A641</t>
+  </si>
+  <si>
+    <t>03182800400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAAD0A</t>
+  </si>
+  <si>
+    <t>03185031600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL67860</t>
+  </si>
+  <si>
+    <t>03611012600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEA24B</t>
+  </si>
+  <si>
+    <t>03612663200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAC165</t>
+  </si>
+  <si>
+    <t>03614275100</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1430,7 @@
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>263</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>91</v>
@@ -1043,7 +1454,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>24.450068312795135</v>
+        <v>24.0988408676588</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>68</v>
@@ -1061,7 +1472,7 @@
         <v>72</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>93</v>
@@ -1070,7 +1481,7 @@
         <v>73</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="U2" t="s" s="0">
         <v>73</v>
@@ -1181,7 +1592,7 @@
         <v>90</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>127</v>
+        <v>264</v>
       </c>
       <c r="BF2" s="1" t="s">
         <v>92</v>
@@ -1219,7 +1630,7 @@
     </row>
     <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>91</v>
@@ -1243,7 +1654,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>24.58441806644632</v>
+        <v>24.600531516221288</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>68</v>
@@ -1261,7 +1672,7 @@
         <v>72</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>93</v>
@@ -1270,7 +1681,7 @@
         <v>73</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="U3" t="s" s="0">
         <v>73</v>
@@ -1381,7 +1792,7 @@
         <v>90</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>129</v>
+        <v>266</v>
       </c>
       <c r="BF3" s="1" t="s">
         <v>110</v>
@@ -1419,7 +1830,7 @@
     </row>
     <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>130</v>
+        <v>267</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>91</v>
@@ -1443,7 +1854,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>24.207824306307835</v>
+        <v>24.226482548087137</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>68</v>
@@ -1461,7 +1872,7 @@
         <v>72</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>93</v>
@@ -1470,7 +1881,7 @@
         <v>75</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="U4" t="s" s="0">
         <v>73</v>
@@ -1581,7 +1992,7 @@
         <v>90</v>
       </c>
       <c r="BE4" s="1" t="s">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="BF4" s="1" t="s">
         <v>111</v>

--- a/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="301">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -826,6 +826,102 @@
   </si>
   <si>
     <t>03614275100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA1F14</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>03130939900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA11DA</t>
+  </si>
+  <si>
+    <t>03132585800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL15577</t>
+  </si>
+  <si>
+    <t>03134340600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLADC2F</t>
+  </si>
+  <si>
+    <t>03869374900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL93F62</t>
+  </si>
+  <si>
+    <t>03870571300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDF7ED</t>
+  </si>
+  <si>
+    <t>03871703500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL81039</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>03129197900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC2A86</t>
+  </si>
+  <si>
+    <t>03130686800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBAA35</t>
+  </si>
+  <si>
+    <t>03137596900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1C249</t>
+  </si>
+  <si>
+    <t>03935202600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD1CEB</t>
+  </si>
+  <si>
+    <t>03936927000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD2F9D</t>
+  </si>
+  <si>
+    <t>03938352500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL36486</t>
+  </si>
+  <si>
+    <t>03582138000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL25974</t>
+  </si>
+  <si>
+    <t>03583371500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3A2C7</t>
+  </si>
+  <si>
+    <t>03584072700</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1526,7 @@
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>91</v>
@@ -1454,7 +1550,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>24.0988408676588</v>
+        <v>24.97572574264472</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>68</v>
@@ -1472,7 +1568,7 @@
         <v>72</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>93</v>
@@ -1481,7 +1577,7 @@
         <v>73</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="U2" t="s" s="0">
         <v>73</v>
@@ -1592,7 +1688,7 @@
         <v>90</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="BF2" s="1" t="s">
         <v>92</v>
@@ -1630,7 +1726,7 @@
     </row>
     <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>91</v>
@@ -1654,7 +1750,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>24.600531516221288</v>
+        <v>24.6310248306423</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>68</v>
@@ -1672,7 +1768,7 @@
         <v>72</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>93</v>
@@ -1681,7 +1777,7 @@
         <v>73</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="U3" t="s" s="0">
         <v>73</v>
@@ -1792,7 +1888,7 @@
         <v>90</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="BF3" s="1" t="s">
         <v>110</v>
@@ -1830,7 +1926,7 @@
     </row>
     <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>91</v>
@@ -1854,7 +1950,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>24.226482548087137</v>
+        <v>24.7635222320858</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>68</v>
@@ -1872,7 +1968,7 @@
         <v>72</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>93</v>
@@ -1881,7 +1977,7 @@
         <v>75</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="U4" t="s" s="0">
         <v>73</v>
@@ -1992,7 +2088,7 @@
         <v>90</v>
       </c>
       <c r="BE4" s="1" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="BF4" s="1" t="s">
         <v>111</v>

--- a/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesPK/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="472">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -922,6 +922,519 @@
   </si>
   <si>
     <t>03584072700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL406CA</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>03628618500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8D7B5</t>
+  </si>
+  <si>
+    <t>03632987800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC9A78</t>
+  </si>
+  <si>
+    <t>03634999400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBF11F</t>
+  </si>
+  <si>
+    <t>03879188600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC06B6</t>
+  </si>
+  <si>
+    <t>03880446900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD2641</t>
+  </si>
+  <si>
+    <t>03881630900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB58CF</t>
+  </si>
+  <si>
+    <t>03109644600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL06EF2</t>
+  </si>
+  <si>
+    <t>03110437600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBA6B6</t>
+  </si>
+  <si>
+    <t>03111052700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL914A1</t>
+  </si>
+  <si>
+    <t>03954920700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBE1EF</t>
+  </si>
+  <si>
+    <t>03956353500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC5BC0</t>
+  </si>
+  <si>
+    <t>03957388300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLACCD8</t>
+  </si>
+  <si>
+    <t>03641587700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9509E</t>
+  </si>
+  <si>
+    <t>03642549900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL121A6</t>
+  </si>
+  <si>
+    <t>03643568300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL05230</t>
+  </si>
+  <si>
+    <t>03049163300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1CCFD</t>
+  </si>
+  <si>
+    <t>03050409100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4BE52</t>
+  </si>
+  <si>
+    <t>03051430300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE1E99</t>
+  </si>
+  <si>
+    <t>03956587300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD3B41</t>
+  </si>
+  <si>
+    <t>03957536000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL271D9</t>
+  </si>
+  <si>
+    <t>03958352000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBBDA2</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>03126467700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA1871</t>
+  </si>
+  <si>
+    <t>03127705600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCA459</t>
+  </si>
+  <si>
+    <t>03128797600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2B0EE</t>
+  </si>
+  <si>
+    <t>03654581800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE2DBA</t>
+  </si>
+  <si>
+    <t>03656664700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCE65C</t>
+  </si>
+  <si>
+    <t>03658642600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9349F</t>
+  </si>
+  <si>
+    <t>03815580500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEECE7</t>
+  </si>
+  <si>
+    <t>03817144100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1C177</t>
+  </si>
+  <si>
+    <t>03818590100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL71BF7</t>
+  </si>
+  <si>
+    <t>03584683800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL46D60</t>
+  </si>
+  <si>
+    <t>03586223500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL44778</t>
+  </si>
+  <si>
+    <t>03587768000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8ACC8</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>03965877300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCEC1F</t>
+  </si>
+  <si>
+    <t>03968108900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6A9A3</t>
+  </si>
+  <si>
+    <t>03969728000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL18A0B</t>
+  </si>
+  <si>
+    <t>03943903100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB4798</t>
+  </si>
+  <si>
+    <t>03945086800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL09297</t>
+  </si>
+  <si>
+    <t>03945972300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6B5E2</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>03422436600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD4260</t>
+  </si>
+  <si>
+    <t>03423140300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL56A60</t>
+  </si>
+  <si>
+    <t>03423721000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL36968</t>
+  </si>
+  <si>
+    <t>03919593400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4028C</t>
+  </si>
+  <si>
+    <t>03920229200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7D966</t>
+  </si>
+  <si>
+    <t>03920864400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA0910</t>
+  </si>
+  <si>
+    <t>03578657500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDD6D8</t>
+  </si>
+  <si>
+    <t>03580228800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL05482</t>
+  </si>
+  <si>
+    <t>03581471700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC7975</t>
+  </si>
+  <si>
+    <t>03601223000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF7026</t>
+  </si>
+  <si>
+    <t>03602473500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC3523</t>
+  </si>
+  <si>
+    <t>03603146800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL59ECE</t>
+  </si>
+  <si>
+    <t>03089111400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCB1BC</t>
+  </si>
+  <si>
+    <t>03091679500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL93E76</t>
+  </si>
+  <si>
+    <t>03092682400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8793F</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>03099660200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL686DC</t>
+  </si>
+  <si>
+    <t>03101344600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL58AEE</t>
+  </si>
+  <si>
+    <t>03102762600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6A92D</t>
+  </si>
+  <si>
+    <t>03327133100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE2A0D</t>
+  </si>
+  <si>
+    <t>03329436900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB96F3</t>
+  </si>
+  <si>
+    <t>03330634900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL890A2</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>03549695400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL37A71</t>
+  </si>
+  <si>
+    <t>03550864700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8AA80</t>
+  </si>
+  <si>
+    <t>03551703100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB37CD</t>
+  </si>
+  <si>
+    <t>03875576100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFF64E</t>
+  </si>
+  <si>
+    <t>03877085900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE8F81</t>
+  </si>
+  <si>
+    <t>03878206500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL39A08</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>03038171500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD7CA1</t>
+  </si>
+  <si>
+    <t>03039318300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL66A81</t>
+  </si>
+  <si>
+    <t>03040148100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL12D32</t>
+  </si>
+  <si>
+    <t>03422773000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF94D5</t>
+  </si>
+  <si>
+    <t>03425241600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2DE7E</t>
+  </si>
+  <si>
+    <t>03426985400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCAD13</t>
+  </si>
+  <si>
+    <t>03341460300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0C937</t>
+  </si>
+  <si>
+    <t>03343262600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5C960</t>
+  </si>
+  <si>
+    <t>03344693700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF365A</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>03681052800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL32AE6</t>
+  </si>
+  <si>
+    <t>03681856100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4E97E</t>
+  </si>
+  <si>
+    <t>03682520700</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEB802</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>03495993600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5E939</t>
+  </si>
+  <si>
+    <t>03497543900</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL64D4F</t>
+  </si>
+  <si>
+    <t>03498871600</t>
   </si>
 </sst>
 </file>
@@ -1526,7 +2039,7 @@
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>91</v>
@@ -1550,7 +2063,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>24.97572574264472</v>
+        <v>24.129919346260646</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>68</v>
@@ -1568,7 +2081,7 @@
         <v>72</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>283</v>
+        <v>466</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>93</v>
@@ -1577,7 +2090,7 @@
         <v>73</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>283</v>
+        <v>466</v>
       </c>
       <c r="U2" t="s" s="0">
         <v>73</v>
@@ -1688,7 +2201,7 @@
         <v>90</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>296</v>
+        <v>467</v>
       </c>
       <c r="BF2" s="1" t="s">
         <v>92</v>
@@ -1726,7 +2239,7 @@
     </row>
     <row r="3" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>297</v>
+        <v>468</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>91</v>
@@ -1750,7 +2263,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>24.6310248306423</v>
+        <v>24.371923103603166</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>68</v>
@@ -1768,7 +2281,7 @@
         <v>72</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>283</v>
+        <v>466</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>93</v>
@@ -1777,7 +2290,7 @@
         <v>73</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>283</v>
+        <v>466</v>
       </c>
       <c r="U3" t="s" s="0">
         <v>73</v>
@@ -1888,7 +2401,7 @@
         <v>90</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>298</v>
+        <v>469</v>
       </c>
       <c r="BF3" s="1" t="s">
         <v>110</v>
@@ -1926,7 +2439,7 @@
     </row>
     <row r="4" spans="1:68" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>299</v>
+        <v>470</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>91</v>
@@ -1950,7 +2463,7 @@
         <v>24.438292084300599</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>24.7635222320858</v>
+        <v>24.887555123177155</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>68</v>
@@ -1968,7 +2481,7 @@
         <v>72</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>283</v>
+        <v>466</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>93</v>
@@ -1977,7 +2490,7 @@
         <v>75</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>283</v>
+        <v>466</v>
       </c>
       <c r="U4" t="s" s="0">
         <v>73</v>
@@ -2088,7 +2601,7 @@
         <v>90</v>
       </c>
       <c r="BE4" s="1" t="s">
-        <v>300</v>
+        <v>471</v>
       </c>
       <c r="BF4" s="1" t="s">
         <v>111</v>
